--- a/Admin/Course Attendance.xlsx
+++ b/Admin/Course Attendance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/851caa7714272873/CLASSES-Informatics/Admin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="400" documentId="13_ncr:1_{10AACCFA-37B1-6D44-A367-828EAD02C19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F91D6B70-303B-3C41-9BD0-206ACC65B30F}"/>
+  <xr:revisionPtr revIDLastSave="406" documentId="13_ncr:1_{10AACCFA-37B1-6D44-A367-828EAD02C19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA632096-A4BE-394E-97BA-C2F9F8397E47}"/>
   <bookViews>
-    <workbookView xWindow="3200" yWindow="2680" windowWidth="27040" windowHeight="16960" xr2:uid="{24CAAD2F-8633-184E-A7D2-D706FBAD8E49}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" activeTab="2" xr2:uid="{24CAAD2F-8633-184E-A7D2-D706FBAD8E49}"/>
   </bookViews>
   <sheets>
     <sheet name="Student Information" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="132">
   <si>
     <t>Class 1</t>
   </si>
@@ -429,6 +429,12 @@
   </si>
   <si>
     <t>Problems in Binary Search, Binary Answers, Queues and Stacks, plus AIO 2023 P4 and P5</t>
+  </si>
+  <si>
+    <t>Review work and Trees</t>
+  </si>
+  <si>
+    <t>Still reviewing work from past units.  Started a little on Trees.</t>
   </si>
 </sst>
 </file>
@@ -2262,9 +2268,24 @@
       <c r="B11" s="6">
         <v>46180</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
+      <c r="C11" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>131</v>
+      </c>
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>

--- a/Admin/Course Attendance.xlsx
+++ b/Admin/Course Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/851caa7714272873/CLASSES-Informatics/Admin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="406" documentId="13_ncr:1_{10AACCFA-37B1-6D44-A367-828EAD02C19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA632096-A4BE-394E-97BA-C2F9F8397E47}"/>
+  <xr:revisionPtr revIDLastSave="409" documentId="13_ncr:1_{10AACCFA-37B1-6D44-A367-828EAD02C19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A39BA65-FE65-554D-A912-ECBBA0213D3B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" activeTab="2" xr2:uid="{24CAAD2F-8633-184E-A7D2-D706FBAD8E49}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="134">
   <si>
     <t>Class 1</t>
   </si>
@@ -435,6 +435,12 @@
   </si>
   <si>
     <t>Still reviewing work from past units.  Started a little on Trees.</t>
+  </si>
+  <si>
+    <t>11:15 - 13:31</t>
+  </si>
+  <si>
+    <t>11:15 - 13:32</t>
   </si>
 </sst>
 </file>
@@ -2300,7 +2306,15 @@
       <c r="B12" s="6">
         <v>46187</v>
       </c>
-      <c r="C12" s="7"/>
+      <c r="C12" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
@@ -2317,7 +2331,18 @@
       <c r="B13" s="6">
         <v>46194</v>
       </c>
-      <c r="C13" s="7"/>
+      <c r="C13" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>

--- a/Admin/Course Attendance.xlsx
+++ b/Admin/Course Attendance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/851caa7714272873/CLASSES-Informatics/Admin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="409" documentId="13_ncr:1_{10AACCFA-37B1-6D44-A367-828EAD02C19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A39BA65-FE65-554D-A912-ECBBA0213D3B}"/>
+  <xr:revisionPtr revIDLastSave="446" documentId="13_ncr:1_{10AACCFA-37B1-6D44-A367-828EAD02C19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F194CFFD-3AE1-5244-B210-375D720C218D}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" activeTab="2" xr2:uid="{24CAAD2F-8633-184E-A7D2-D706FBAD8E49}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="18460" windowHeight="16960" activeTab="3" xr2:uid="{24CAAD2F-8633-184E-A7D2-D706FBAD8E49}"/>
   </bookViews>
   <sheets>
     <sheet name="Student Information" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="141">
   <si>
     <t>Class 1</t>
   </si>
@@ -320,12 +320,6 @@
     <t>Reddam House School Sydney</t>
   </si>
   <si>
-    <t>Chuyuan Chou</t>
-  </si>
-  <si>
-    <t>12:30 - 14:30</t>
-  </si>
-  <si>
     <t>xxx</t>
   </si>
   <si>
@@ -441,6 +435,33 @@
   </si>
   <si>
     <t>11:15 - 13:32</t>
+  </si>
+  <si>
+    <t>Jayden Pan</t>
+  </si>
+  <si>
+    <t>Daiyan Fayez</t>
+  </si>
+  <si>
+    <t>Ethan Zhao</t>
+  </si>
+  <si>
+    <t>Zara Feng</t>
+  </si>
+  <si>
+    <t>Pymble Ladies College</t>
+  </si>
+  <si>
+    <t>Gavin Gao</t>
+  </si>
+  <si>
+    <t>Liam Ke</t>
+  </si>
+  <si>
+    <t>North Rocks Public School</t>
+  </si>
+  <si>
+    <t>13:30 - 15:30</t>
   </si>
 </sst>
 </file>
@@ -917,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91FB8569-CA3E-974B-8804-A3AC313A4BC3}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -942,7 +963,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,7 +980,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -976,7 +997,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -993,7 +1014,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -1010,7 +1031,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>85</v>
       </c>
@@ -1021,13 +1042,13 @@
         <v>23</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E6">
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>90</v>
       </c>
@@ -1038,13 +1059,13 @@
         <v>86</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E7">
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>91</v>
       </c>
@@ -1055,15 +1076,15 @@
         <v>86</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E8">
         <v>2026</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B9">
         <v>7</v>
@@ -1072,13 +1093,13 @@
         <v>92</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E9">
         <v>2026</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>87</v>
       </c>
@@ -1089,77 +1110,149 @@
         <v>88</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E10">
         <v>2026</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B11">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>2026</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B12">
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E12">
         <v>2026</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B13">
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E13">
         <v>2026</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B14">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E14">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="E16">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="E17">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="E18">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>136</v>
+      </c>
+      <c r="E19">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20">
         <v>2026</v>
       </c>
     </row>
@@ -2007,10 +2100,10 @@
         <v>16</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H2" s="11" t="s">
         <v>35</v>
@@ -2047,10 +2140,10 @@
         <v>4</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
@@ -2079,10 +2172,10 @@
         <v>4</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
@@ -2099,7 +2192,7 @@
         <v>46138</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>4</v>
@@ -2108,7 +2201,7 @@
         <v>4</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -2126,7 +2219,7 @@
         <v>46145</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>4</v>
@@ -2135,7 +2228,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -2153,7 +2246,7 @@
         <v>46152</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>4</v>
@@ -2165,7 +2258,7 @@
         <v>4</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -2183,19 +2276,19 @@
         <v>46159</v>
       </c>
       <c r="C8" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>120</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>122</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -2213,7 +2306,7 @@
         <v>46166</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>4</v>
@@ -2225,7 +2318,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -2237,13 +2330,13 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B10" s="6">
         <v>46173</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>4</v>
@@ -2258,7 +2351,7 @@
         <v>69</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
@@ -2269,13 +2362,13 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B11" s="6">
         <v>46180</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>4</v>
@@ -2287,10 +2380,10 @@
         <v>4</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
@@ -2301,13 +2394,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B12" s="6">
         <v>46187</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>4</v>
@@ -2326,13 +2419,13 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B13" s="6">
         <v>46194</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>4</v>
@@ -2354,12 +2447,23 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B14" s="6">
         <v>46201</v>
       </c>
-      <c r="C14" s="7"/>
+      <c r="C14" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
@@ -2561,7 +2665,7 @@
   <sheetData>
     <row r="1" spans="1:19" s="15" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="14"/>
@@ -2591,28 +2695,28 @@
         <v>3</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="H2" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="K2" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>104</v>
       </c>
       <c r="L2" s="11" t="s">
         <v>35</v>
@@ -2634,25 +2738,13 @@
         <v>0</v>
       </c>
       <c r="B3" s="6">
-        <v>46109</v>
+        <v>46229</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>4</v>
+        <v>140</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
@@ -2779,17 +2871,17 @@
       <c r="R12" s="8"/>
       <c r="S12" s="8"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7"/>
       <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
       <c r="S13" s="8"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
@@ -2797,7 +2889,6 @@
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
       <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -2810,7 +2901,6 @@
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
       <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
       <c r="N15" s="8"/>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
@@ -2822,7 +2912,6 @@
       <c r="B16" s="6"/>
       <c r="C16" s="7"/>
       <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
       <c r="N16" s="8"/>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -2835,7 +2924,6 @@
       <c r="B17" s="6"/>
       <c r="C17" s="7"/>
       <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
       <c r="N17" s="8"/>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
@@ -2848,7 +2936,6 @@
       <c r="B18" s="6"/>
       <c r="C18" s="7"/>
       <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
       <c r="N18" s="8"/>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>

--- a/Admin/Course Attendance.xlsx
+++ b/Admin/Course Attendance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/851caa7714272873/CLASSES-Informatics/Admin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="446" documentId="13_ncr:1_{10AACCFA-37B1-6D44-A367-828EAD02C19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F194CFFD-3AE1-5244-B210-375D720C218D}"/>
+  <xr:revisionPtr revIDLastSave="466" documentId="13_ncr:1_{10AACCFA-37B1-6D44-A367-828EAD02C19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2E7BD95-6FAE-B246-A5C8-5394732BDE58}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="18460" windowHeight="16960" activeTab="3" xr2:uid="{24CAAD2F-8633-184E-A7D2-D706FBAD8E49}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="25740" windowHeight="15720" xr2:uid="{24CAAD2F-8633-184E-A7D2-D706FBAD8E49}"/>
   </bookViews>
   <sheets>
     <sheet name="Student Information" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="154">
   <si>
     <t>Class 1</t>
   </si>
@@ -462,6 +462,45 @@
   </si>
   <si>
     <t>13:30 - 15:30</t>
+  </si>
+  <si>
+    <t>jayden.pan618@gmail.com</t>
+  </si>
+  <si>
+    <t>fayez77@hotmail.com</t>
+  </si>
+  <si>
+    <t>ethan.zhao0505@gmail.com</t>
+  </si>
+  <si>
+    <t>gavin.tao.gao@gmail.com</t>
+  </si>
+  <si>
+    <t>zfeng2031@pymblelc.nsw.edu.au</t>
+  </si>
+  <si>
+    <t>liambeiyuke@gmail.com</t>
+  </si>
+  <si>
+    <t>amy.zang777@gmail.com</t>
+  </si>
+  <si>
+    <t>Lindfield East Public School</t>
+  </si>
+  <si>
+    <t>Leumeah Public School</t>
+  </si>
+  <si>
+    <t>North Sydney Boys High School</t>
+  </si>
+  <si>
+    <t>Dural Public School</t>
+  </si>
+  <si>
+    <t>Amy Zang</t>
+  </si>
+  <si>
+    <t>Thornleigh West Public School</t>
   </si>
 </sst>
 </file>
@@ -938,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91FB8569-CA3E-974B-8804-A3AC313A4BC3}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -963,7 +1002,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -980,7 +1019,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -997,7 +1036,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1014,7 +1053,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -1031,7 +1070,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>85</v>
       </c>
@@ -1048,7 +1087,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>90</v>
       </c>
@@ -1065,7 +1104,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>91</v>
       </c>
@@ -1082,7 +1121,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>110</v>
       </c>
@@ -1099,7 +1138,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>87</v>
       </c>
@@ -1116,7 +1155,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>95</v>
       </c>
@@ -1133,7 +1172,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>115</v>
       </c>
@@ -1150,7 +1189,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>102</v>
       </c>
@@ -1167,7 +1206,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>106</v>
       </c>
@@ -1191,6 +1230,12 @@
       <c r="B15">
         <v>6</v>
       </c>
+      <c r="C15" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>141</v>
+      </c>
       <c r="E15">
         <v>2026</v>
       </c>
@@ -1202,6 +1247,12 @@
       <c r="B16">
         <v>6</v>
       </c>
+      <c r="C16" t="s">
+        <v>149</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="E16">
         <v>2026</v>
       </c>
@@ -1213,6 +1264,12 @@
       <c r="B17">
         <v>8</v>
       </c>
+      <c r="C17" t="s">
+        <v>150</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>143</v>
+      </c>
       <c r="E17">
         <v>2026</v>
       </c>
@@ -1224,6 +1281,12 @@
       <c r="B18">
         <v>6</v>
       </c>
+      <c r="C18" t="s">
+        <v>151</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>144</v>
+      </c>
       <c r="E18">
         <v>2026</v>
       </c>
@@ -1238,6 +1301,9 @@
       <c r="C19" t="s">
         <v>136</v>
       </c>
+      <c r="D19" s="16" t="s">
+        <v>145</v>
+      </c>
       <c r="E19">
         <v>2026</v>
       </c>
@@ -1252,7 +1318,27 @@
       <c r="C20" t="s">
         <v>139</v>
       </c>
+      <c r="D20" s="16" t="s">
+        <v>146</v>
+      </c>
       <c r="E20">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>153</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="E21">
         <v>2026</v>
       </c>
     </row>
@@ -1271,6 +1357,13 @@
     <hyperlink ref="D7" r:id="rId11" xr:uid="{1ABF355E-0D8F-084E-ACFD-5DBC444456A1}"/>
     <hyperlink ref="D8" r:id="rId12" xr:uid="{A93494F7-BC6D-1E43-A2C9-7DEE17299473}"/>
     <hyperlink ref="D10" r:id="rId13" xr:uid="{18CF6544-FA5E-2E41-BFF4-3292E3CA7780}"/>
+    <hyperlink ref="D15" r:id="rId14" xr:uid="{925B2C00-DB4F-4AFB-A4D3-33BF3BA8235B}"/>
+    <hyperlink ref="D16" r:id="rId15" xr:uid="{8ADFBE63-3696-4775-9D85-1329B292DB9E}"/>
+    <hyperlink ref="D17" r:id="rId16" xr:uid="{EE2C7F52-F790-403A-B8AD-8AD5639268DE}"/>
+    <hyperlink ref="D18" r:id="rId17" xr:uid="{B337F136-0219-43C2-B86C-E31C86F9FC00}"/>
+    <hyperlink ref="D20" r:id="rId18" xr:uid="{DBB3C7ED-BF02-4317-AAE3-D4789EB2AB81}"/>
+    <hyperlink ref="D21" r:id="rId19" xr:uid="{1AC52EE6-8031-4E61-97BC-A16EE2F31BE4}"/>
+    <hyperlink ref="D19" r:id="rId20" xr:uid="{5952183A-29A7-409D-93BF-AA0EF92E7186}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2652,18 +2745,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DFCB767-1FBD-9647-82C4-2908A24D9134}">
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.1640625" style="4" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="4" customWidth="1"/>
     <col min="3" max="3" width="13.33203125" style="3" customWidth="1"/>
-    <col min="4" max="11" width="3.83203125" style="3" customWidth="1"/>
-    <col min="12" max="17" width="15.83203125" style="3" customWidth="1"/>
-    <col min="18" max="16384" width="10.83203125" style="4"/>
+    <col min="4" max="12" width="3.83203125" style="3" customWidth="1"/>
+    <col min="13" max="18" width="15.83203125" style="3" customWidth="1"/>
+    <col min="19" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="15" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" s="15" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>94</v>
       </c>
@@ -2683,8 +2776,9 @@
       <c r="O1" s="14"/>
       <c r="P1" s="14"/>
       <c r="Q1" s="14"/>
-    </row>
-    <row r="2" spans="1:19" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R1" s="14"/>
+    </row>
+    <row r="2" spans="1:20" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -2718,22 +2812,25 @@
       <c r="K2" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="M2" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="N2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="11"/>
       <c r="O2" s="11"/>
       <c r="P2" s="11"/>
       <c r="Q2" s="11"/>
       <c r="R2" s="11"/>
-      <c r="S2" s="11" t="s">
+      <c r="S2" s="11"/>
+      <c r="T2" s="11" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -2743,22 +2840,48 @@
       <c r="C3" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M3" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M3" s="8"/>
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
       <c r="S3" s="8"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T3" s="8"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
       <c r="B4" s="6"/>
       <c r="C4" s="7"/>
-      <c r="L4" s="8"/>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
@@ -2766,12 +2889,12 @@
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
       <c r="S4" s="8"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T4" s="8"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
       <c r="C5" s="7"/>
-      <c r="L5" s="8"/>
       <c r="M5" s="8"/>
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
@@ -2779,12 +2902,12 @@
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
       <c r="S5" s="8"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T5" s="8"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="7"/>
-      <c r="L6" s="8"/>
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
@@ -2792,12 +2915,12 @@
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
       <c r="S6" s="8"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T6" s="8"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
       <c r="C7" s="7"/>
-      <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
@@ -2805,12 +2928,12 @@
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="8"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7"/>
-      <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
@@ -2818,12 +2941,12 @@
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
       <c r="S8" s="8"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="8"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
-      <c r="L9" s="8"/>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
@@ -2831,12 +2954,12 @@
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
       <c r="S9" s="8"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="8"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7"/>
-      <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
@@ -2844,12 +2967,12 @@
       <c r="Q10" s="8"/>
       <c r="R10" s="8"/>
       <c r="S10" s="8"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="8"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7"/>
-      <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
@@ -2857,12 +2980,12 @@
       <c r="Q11" s="8"/>
       <c r="R11" s="8"/>
       <c r="S11" s="8"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="8"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7"/>
-      <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
       <c r="O12" s="8"/>
@@ -2870,198 +2993,199 @@
       <c r="Q12" s="8"/>
       <c r="R12" s="8"/>
       <c r="S12" s="8"/>
-    </row>
-    <row r="13" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="T12" s="8"/>
+    </row>
+    <row r="13" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="1"/>
+      <c r="M13" s="8"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
-      <c r="S13" s="8"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S13" s="1"/>
+      <c r="T13" s="8"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
-      <c r="L14" s="8"/>
-      <c r="N14" s="8"/>
+      <c r="M14" s="8"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
       <c r="R14" s="8"/>
       <c r="S14" s="8"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="8"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
-      <c r="L15" s="8"/>
-      <c r="N15" s="8"/>
+      <c r="M15" s="8"/>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S15" s="8"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="7"/>
-      <c r="L16" s="8"/>
-      <c r="N16" s="8"/>
+      <c r="M16" s="8"/>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
       <c r="S16" s="8"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="8"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7"/>
-      <c r="L17" s="8"/>
-      <c r="N17" s="8"/>
+      <c r="M17" s="8"/>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
       <c r="R17" s="8"/>
       <c r="S17" s="8"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="8"/>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="7"/>
-      <c r="L18" s="8"/>
-      <c r="N18" s="8"/>
+      <c r="M18" s="8"/>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
       <c r="R18" s="8"/>
       <c r="S18" s="8"/>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="8"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="7"/>
-      <c r="L19" s="8"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S19" s="8"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="7"/>
-      <c r="L20" s="8"/>
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
       <c r="R20" s="8"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S20" s="8"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7"/>
-      <c r="L21" s="8"/>
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
       <c r="R21" s="8"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S21" s="8"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" s="5"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7"/>
-      <c r="L22" s="8"/>
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
       <c r="O22" s="8"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="8"/>
       <c r="R22" s="8"/>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S22" s="8"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" s="5"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7"/>
-      <c r="L23" s="8"/>
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
       <c r="R23" s="8"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S23" s="8"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" s="5"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7"/>
-      <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
       <c r="R24" s="8"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S24" s="8"/>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" s="5"/>
       <c r="B25" s="6"/>
       <c r="C25" s="7"/>
-      <c r="L25" s="8"/>
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
       <c r="O25" s="8"/>
       <c r="P25" s="8"/>
       <c r="Q25" s="8"/>
       <c r="R25" s="8"/>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S25" s="8"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" s="5"/>
       <c r="B26" s="6"/>
       <c r="C26" s="7"/>
-      <c r="L26" s="8"/>
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
       <c r="Q26" s="8"/>
       <c r="R26" s="8"/>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S26" s="8"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" s="5"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7"/>
-      <c r="L27" s="8"/>
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
       <c r="Q27" s="8"/>
       <c r="R27" s="8"/>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S27" s="8"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" s="5"/>
       <c r="B28" s="6"/>
       <c r="C28" s="7"/>
-      <c r="L28" s="8"/>
       <c r="M28" s="8"/>
       <c r="N28" s="8"/>
       <c r="O28" s="8"/>
       <c r="P28" s="8"/>
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
+      <c r="S28" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Admin/Course Attendance.xlsx
+++ b/Admin/Course Attendance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/851caa7714272873/CLASSES-Informatics/Admin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="466" documentId="13_ncr:1_{10AACCFA-37B1-6D44-A367-828EAD02C19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2E7BD95-6FAE-B246-A5C8-5394732BDE58}"/>
+  <xr:revisionPtr revIDLastSave="480" documentId="13_ncr:1_{10AACCFA-37B1-6D44-A367-828EAD02C19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F237102B-B8AE-2146-A24A-5A2588C80088}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="25740" windowHeight="15720" xr2:uid="{24CAAD2F-8633-184E-A7D2-D706FBAD8E49}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="25740" windowHeight="15720" activeTab="1" xr2:uid="{24CAAD2F-8633-184E-A7D2-D706FBAD8E49}"/>
   </bookViews>
   <sheets>
     <sheet name="Student Information" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="153">
   <si>
     <t>Class 1</t>
   </si>
@@ -431,12 +431,6 @@
     <t>Still reviewing work from past units.  Started a little on Trees.</t>
   </si>
   <si>
-    <t>11:15 - 13:31</t>
-  </si>
-  <si>
-    <t>11:15 - 13:32</t>
-  </si>
-  <si>
     <t>Jayden Pan</t>
   </si>
   <si>
@@ -501,6 +495,9 @@
   </si>
   <si>
     <t>Thornleigh West Public School</t>
+  </si>
+  <si>
+    <t>Class 13</t>
   </si>
 </sst>
 </file>
@@ -1225,16 +1222,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B15">
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E15">
         <v>2026</v>
@@ -1242,16 +1239,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B16">
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E16">
         <v>2026</v>
@@ -1259,16 +1256,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B17">
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E17">
         <v>2026</v>
@@ -1276,16 +1273,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B18">
         <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E18">
         <v>2026</v>
@@ -1293,16 +1290,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B19">
         <v>7</v>
       </c>
       <c r="C19" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E19">
         <v>2026</v>
@@ -1310,16 +1307,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B20">
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E20">
         <v>2026</v>
@@ -1327,16 +1324,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E21">
         <v>2026</v>
@@ -2493,7 +2490,7 @@
         <v>46187</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>4</v>
@@ -2518,7 +2515,7 @@
         <v>46194</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>4</v>
@@ -2546,7 +2543,7 @@
         <v>46201</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
@@ -2567,9 +2564,24 @@
       <c r="O14" s="8"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="7"/>
+      <c r="A15" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B15" s="6">
+        <v>46236</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
@@ -2789,22 +2801,22 @@
         <v>3</v>
       </c>
       <c r="D2" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="G2" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="H2" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>135</v>
-      </c>
       <c r="I2" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J2" s="10" t="s">
         <v>97</v>
@@ -2813,7 +2825,7 @@
         <v>87</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>35</v>
@@ -2838,7 +2850,7 @@
         <v>46229</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>4</v>
@@ -2879,9 +2891,39 @@
       <c r="T3" s="8"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A4" s="5"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6">
+        <v>46236</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>

--- a/Admin/Course Attendance.xlsx
+++ b/Admin/Course Attendance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/851caa7714272873/CLASSES-Informatics/Admin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="480" documentId="13_ncr:1_{10AACCFA-37B1-6D44-A367-828EAD02C19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F237102B-B8AE-2146-A24A-5A2588C80088}"/>
+  <xr:revisionPtr revIDLastSave="527" documentId="13_ncr:1_{10AACCFA-37B1-6D44-A367-828EAD02C19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C59B26C-DB70-4287-9D08-3A9620C2AC17}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="25740" windowHeight="15720" activeTab="1" xr2:uid="{24CAAD2F-8633-184E-A7D2-D706FBAD8E49}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" activeTab="3" xr2:uid="{24CAAD2F-8633-184E-A7D2-D706FBAD8E49}"/>
   </bookViews>
   <sheets>
     <sheet name="Student Information" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="166">
   <si>
     <t>Class 1</t>
   </si>
@@ -498,6 +498,45 @@
   </si>
   <si>
     <t>Class 13</t>
+  </si>
+  <si>
+    <t>Shaurya Thakur</t>
+  </si>
+  <si>
+    <t>Hornsby North Public School</t>
+  </si>
+  <si>
+    <t>Aiden Wang</t>
+  </si>
+  <si>
+    <t>lyr8322@gmail.com</t>
+  </si>
+  <si>
+    <t>Samuel Gilbert Public School</t>
+  </si>
+  <si>
+    <t>Sean Mok</t>
+  </si>
+  <si>
+    <t>sean.mok484@education.nsw.gov.au</t>
+  </si>
+  <si>
+    <t>Baulkham Hills North Public School</t>
+  </si>
+  <si>
+    <t>Class 14</t>
+  </si>
+  <si>
+    <t>Simulation and Binary Trees</t>
+  </si>
+  <si>
+    <t>Simulation with 2022 problems, Binary tree representation, complete binary trees, binary tree traversal</t>
+  </si>
+  <si>
+    <t>First Encounter, Know the Variables</t>
+  </si>
+  <si>
+    <t>Know the Variables, review homework</t>
   </si>
 </sst>
 </file>
@@ -546,6 +585,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -974,15 +1014,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91FB8569-CA3E-974B-8804-A3AC313A4BC3}">
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="3" max="3" width="33.83203125" customWidth="1"/>
-    <col min="4" max="4" width="36.83203125" customWidth="1"/>
+    <col min="3" max="3" width="33.85546875" customWidth="1"/>
+    <col min="4" max="4" width="36.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -999,7 +1039,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,7 +1056,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -1033,7 +1073,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1050,7 +1090,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -1067,7 +1107,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>85</v>
       </c>
@@ -1084,7 +1124,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>90</v>
       </c>
@@ -1101,7 +1141,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>91</v>
       </c>
@@ -1118,7 +1158,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>110</v>
       </c>
@@ -1135,7 +1175,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>87</v>
       </c>
@@ -1152,7 +1192,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>95</v>
       </c>
@@ -1169,7 +1209,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>115</v>
       </c>
@@ -1186,7 +1226,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>102</v>
       </c>
@@ -1203,7 +1243,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>106</v>
       </c>
@@ -1220,7 +1260,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>130</v>
       </c>
@@ -1237,7 +1277,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>131</v>
       </c>
@@ -1254,7 +1294,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>132</v>
       </c>
@@ -1271,7 +1311,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>135</v>
       </c>
@@ -1288,7 +1328,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>133</v>
       </c>
@@ -1305,7 +1345,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>136</v>
       </c>
@@ -1322,7 +1362,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>150</v>
       </c>
@@ -1337,6 +1377,51 @@
       </c>
       <c r="E21">
         <v>2026</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>154</v>
+      </c>
+      <c r="E22">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23">
+        <v>5</v>
+      </c>
+      <c r="C23" t="s">
+        <v>157</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="E23">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -1369,17 +1454,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05115B71-C326-1145-853C-2345070572D9}">
   <dimension ref="A1:P28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="12.9" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1640625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="3" customWidth="1"/>
-    <col min="4" max="8" width="3.83203125" style="3" customWidth="1"/>
-    <col min="9" max="14" width="15.83203125" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="10.83203125" style="4"/>
+    <col min="3" max="3" width="13.35546875" style="3" customWidth="1"/>
+    <col min="4" max="8" width="3.85546875" style="3" customWidth="1"/>
+    <col min="9" max="14" width="15.85546875" style="3" customWidth="1"/>
+    <col min="15" max="16384" width="10.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="15" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" s="15" customFormat="1" ht="31.75" x14ac:dyDescent="0.45">
       <c r="A1" s="13" t="s">
         <v>5</v>
       </c>
@@ -1397,7 +1482,7 @@
       <c r="M1" s="14"/>
       <c r="N1" s="14"/>
     </row>
-    <row r="2" spans="1:16" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="80.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -1437,7 +1522,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -1479,7 +1564,7 @@
       </c>
       <c r="P3" s="8"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
@@ -1508,7 +1593,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
         <v>0</v>
       </c>
@@ -1547,7 +1632,7 @@
       </c>
       <c r="P5" s="8"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6" s="5" t="s">
         <v>26</v>
       </c>
@@ -1574,7 +1659,7 @@
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
@@ -1607,7 +1692,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
@@ -1638,7 +1723,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9" s="5" t="s">
         <v>26</v>
       </c>
@@ -1671,7 +1756,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10" s="5" t="s">
         <v>29</v>
       </c>
@@ -1702,7 +1787,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11" s="5" t="s">
         <v>28</v>
       </c>
@@ -1735,7 +1820,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12" s="5" t="s">
         <v>31</v>
       </c>
@@ -1768,7 +1853,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13" s="5" t="s">
         <v>33</v>
       </c>
@@ -1792,7 +1877,7 @@
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14" s="5" t="s">
         <v>34</v>
       </c>
@@ -1831,7 +1916,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15" s="5" t="s">
         <v>79</v>
       </c>
@@ -1854,7 +1939,7 @@
       <c r="N15" s="8"/>
       <c r="O15" s="8"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A16" s="5" t="s">
         <v>0</v>
       </c>
@@ -1888,7 +1973,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
@@ -1917,7 +2002,7 @@
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A18" s="5" t="s">
         <v>26</v>
       </c>
@@ -1946,7 +2031,7 @@
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A19" s="5" t="s">
         <v>28</v>
       </c>
@@ -1975,7 +2060,7 @@
       <c r="N19" s="8"/>
       <c r="O19" s="8"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A20" s="5" t="s">
         <v>29</v>
       </c>
@@ -2003,7 +2088,7 @@
       <c r="N20" s="8"/>
       <c r="O20" s="8"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A21" s="5" t="s">
         <v>31</v>
       </c>
@@ -2034,7 +2119,7 @@
       <c r="N21" s="8"/>
       <c r="O21" s="8"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A22" s="5" t="s">
         <v>34</v>
       </c>
@@ -2065,7 +2150,7 @@
       <c r="N22" s="8"/>
       <c r="O22" s="8"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A23" s="5"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7"/>
@@ -2077,7 +2162,7 @@
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A24" s="5"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7"/>
@@ -2089,7 +2174,7 @@
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A25" s="5"/>
       <c r="B25" s="6"/>
       <c r="C25" s="7"/>
@@ -2101,7 +2186,7 @@
       <c r="N25" s="8"/>
       <c r="O25" s="8"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A26" s="5"/>
       <c r="B26" s="6"/>
       <c r="C26" s="7"/>
@@ -2113,7 +2198,7 @@
       <c r="N26" s="8"/>
       <c r="O26" s="8"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A27" s="5"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7"/>
@@ -2125,7 +2210,7 @@
       <c r="N27" s="8"/>
       <c r="O27" s="8"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A28" s="5"/>
       <c r="B28" s="6"/>
       <c r="C28" s="7"/>
@@ -2146,17 +2231,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1940DD8-A835-C84C-9FD6-C7272FA36228}">
   <dimension ref="A1:O28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="12.9" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1640625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="3" customWidth="1"/>
-    <col min="4" max="7" width="3.83203125" style="3" customWidth="1"/>
-    <col min="8" max="13" width="15.83203125" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="10.83203125" style="4"/>
+    <col min="3" max="3" width="13.35546875" style="3" customWidth="1"/>
+    <col min="4" max="7" width="3.85546875" style="3" customWidth="1"/>
+    <col min="8" max="13" width="15.85546875" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="10.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="15" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="15" customFormat="1" ht="31.75" x14ac:dyDescent="0.45">
       <c r="A1" s="13" t="s">
         <v>89</v>
       </c>
@@ -2173,7 +2258,7 @@
       <c r="L1" s="14"/>
       <c r="M1" s="14"/>
     </row>
-    <row r="2" spans="1:15" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="80.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -2210,7 +2295,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -2242,7 +2327,7 @@
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
@@ -2274,7 +2359,7 @@
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
         <v>26</v>
       </c>
@@ -2301,7 +2386,7 @@
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" s="5" t="s">
         <v>28</v>
       </c>
@@ -2328,7 +2413,7 @@
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" s="5" t="s">
         <v>29</v>
       </c>
@@ -2358,7 +2443,7 @@
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A8" s="5" t="s">
         <v>31</v>
       </c>
@@ -2388,7 +2473,7 @@
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9" s="5" t="s">
         <v>34</v>
       </c>
@@ -2418,7 +2503,7 @@
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" s="5" t="s">
         <v>122</v>
       </c>
@@ -2450,7 +2535,7 @@
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11" s="5" t="s">
         <v>123</v>
       </c>
@@ -2482,7 +2567,7 @@
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" s="5" t="s">
         <v>124</v>
       </c>
@@ -2507,7 +2592,7 @@
       <c r="N12" s="8"/>
       <c r="O12" s="8"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" s="5" t="s">
         <v>125</v>
       </c>
@@ -2535,7 +2620,7 @@
       <c r="N13" s="8"/>
       <c r="O13" s="8"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" s="5" t="s">
         <v>126</v>
       </c>
@@ -2563,7 +2648,7 @@
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A15" s="5" t="s">
         <v>152</v>
       </c>
@@ -2590,12 +2675,28 @@
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A16" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" s="6">
+        <v>46243</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>163</v>
+      </c>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -2603,7 +2704,7 @@
       <c r="N16" s="8"/>
       <c r="O16" s="8"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7"/>
@@ -2616,7 +2717,7 @@
       <c r="N17" s="8"/>
       <c r="O17" s="8"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="7"/>
@@ -2629,7 +2730,7 @@
       <c r="N18" s="8"/>
       <c r="O18" s="8"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="7"/>
@@ -2641,7 +2742,7 @@
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="7"/>
@@ -2653,7 +2754,7 @@
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A21" s="5"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7"/>
@@ -2665,7 +2766,7 @@
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A22" s="5"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7"/>
@@ -2677,7 +2778,7 @@
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A23" s="5"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7"/>
@@ -2689,7 +2790,7 @@
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A24" s="5"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7"/>
@@ -2701,7 +2802,7 @@
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A25" s="5"/>
       <c r="B25" s="6"/>
       <c r="C25" s="7"/>
@@ -2713,7 +2814,7 @@
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A26" s="5"/>
       <c r="B26" s="6"/>
       <c r="C26" s="7"/>
@@ -2725,7 +2826,7 @@
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A27" s="5"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7"/>
@@ -2737,7 +2838,7 @@
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A28" s="5"/>
       <c r="B28" s="6"/>
       <c r="C28" s="7"/>
@@ -2758,17 +2859,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DFCB767-1FBD-9647-82C4-2908A24D9134}">
   <dimension ref="A1:T28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="12.9" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1640625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="3" customWidth="1"/>
-    <col min="4" max="12" width="3.83203125" style="3" customWidth="1"/>
-    <col min="13" max="18" width="15.83203125" style="3" customWidth="1"/>
-    <col min="19" max="16384" width="10.83203125" style="4"/>
+    <col min="3" max="3" width="13.35546875" style="3" customWidth="1"/>
+    <col min="4" max="14" width="3.85546875" style="3" customWidth="1"/>
+    <col min="15" max="18" width="15.85546875" style="3" customWidth="1"/>
+    <col min="19" max="16384" width="10.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="15" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" s="15" customFormat="1" ht="31.75" x14ac:dyDescent="0.45">
       <c r="A1" s="13" t="s">
         <v>94</v>
       </c>
@@ -2790,7 +2891,7 @@
       <c r="Q1" s="14"/>
       <c r="R1" s="14"/>
     </row>
-    <row r="2" spans="1:20" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" ht="80.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -2827,11 +2928,11 @@
       <c r="L2" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="M2" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>36</v>
+      <c r="M2" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>158</v>
       </c>
       <c r="O2" s="11"/>
       <c r="P2" s="11"/>
@@ -2842,7 +2943,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -2879,20 +2980,18 @@
       <c r="L3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="O3" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
       <c r="S3" s="8"/>
       <c r="T3" s="8"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B4" s="6">
         <v>46236</v>
@@ -2924,34 +3023,68 @@
       <c r="L4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
+      <c r="O4" s="8" t="s">
+        <v>164</v>
+      </c>
       <c r="P4" s="8"/>
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
       <c r="S4" s="8"/>
       <c r="T4" s="8"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="7"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="6">
+        <v>46243</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>165</v>
+      </c>
       <c r="P5" s="8"/>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
       <c r="S5" s="8"/>
       <c r="T5" s="8"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="7"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
@@ -2959,12 +3092,10 @@
       <c r="S6" s="8"/>
       <c r="T6" s="8"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
       <c r="C7" s="7"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
@@ -2972,12 +3103,10 @@
       <c r="S7" s="8"/>
       <c r="T7" s="8"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
@@ -2985,12 +3114,10 @@
       <c r="S8" s="8"/>
       <c r="T8" s="8"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
@@ -2998,12 +3125,10 @@
       <c r="S9" s="8"/>
       <c r="T9" s="8"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
       <c r="Q10" s="8"/>
@@ -3011,12 +3136,10 @@
       <c r="S10" s="8"/>
       <c r="T10" s="8"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
       <c r="Q11" s="8"/>
@@ -3024,12 +3147,10 @@
       <c r="S11" s="8"/>
       <c r="T11" s="8"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
       <c r="Q12" s="8"/>
@@ -3037,12 +3158,10 @@
       <c r="S12" s="8"/>
       <c r="T12" s="8"/>
     </row>
-    <row r="13" spans="1:20" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" ht="15.9" x14ac:dyDescent="0.45">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
@@ -3050,11 +3169,10 @@
       <c r="S13" s="1"/>
       <c r="T13" s="8"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
-      <c r="M14" s="8"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
@@ -3062,22 +3180,20 @@
       <c r="S14" s="8"/>
       <c r="T14" s="8"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
-      <c r="M15" s="8"/>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
       <c r="S15" s="8"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="7"/>
-      <c r="M16" s="8"/>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
@@ -3085,11 +3201,10 @@
       <c r="S16" s="8"/>
       <c r="T16" s="8"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7"/>
-      <c r="M17" s="8"/>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
@@ -3097,11 +3212,10 @@
       <c r="S17" s="8"/>
       <c r="T17" s="8"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="7"/>
-      <c r="M18" s="8"/>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
@@ -3109,120 +3223,100 @@
       <c r="S18" s="8"/>
       <c r="T18" s="8"/>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="7"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
       <c r="S19" s="8"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="7"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
       <c r="R20" s="8"/>
       <c r="S20" s="8"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A21" s="5"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
       <c r="R21" s="8"/>
       <c r="S21" s="8"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A22" s="5"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
       <c r="O22" s="8"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="8"/>
       <c r="R22" s="8"/>
       <c r="S22" s="8"/>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A23" s="5"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
       <c r="R23" s="8"/>
       <c r="S23" s="8"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A24" s="5"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
       <c r="R24" s="8"/>
       <c r="S24" s="8"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A25" s="5"/>
       <c r="B25" s="6"/>
       <c r="C25" s="7"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
       <c r="O25" s="8"/>
       <c r="P25" s="8"/>
       <c r="Q25" s="8"/>
       <c r="R25" s="8"/>
       <c r="S25" s="8"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A26" s="5"/>
       <c r="B26" s="6"/>
       <c r="C26" s="7"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
       <c r="Q26" s="8"/>
       <c r="R26" s="8"/>
       <c r="S26" s="8"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A27" s="5"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
       <c r="Q27" s="8"/>
       <c r="R27" s="8"/>
       <c r="S27" s="8"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A28" s="5"/>
       <c r="B28" s="6"/>
       <c r="C28" s="7"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
       <c r="O28" s="8"/>
       <c r="P28" s="8"/>
       <c r="Q28" s="8"/>

--- a/Admin/Course Attendance.xlsx
+++ b/Admin/Course Attendance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/851caa7714272873/CLASSES-Informatics/Admin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="527" documentId="13_ncr:1_{10AACCFA-37B1-6D44-A367-828EAD02C19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C59B26C-DB70-4287-9D08-3A9620C2AC17}"/>
+  <xr:revisionPtr revIDLastSave="583" documentId="13_ncr:1_{10AACCFA-37B1-6D44-A367-828EAD02C19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A79DAE5-37B7-6D41-B2ED-CEF06E20A041}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" activeTab="3" xr2:uid="{24CAAD2F-8633-184E-A7D2-D706FBAD8E49}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="29940" windowHeight="16700" xr2:uid="{24CAAD2F-8633-184E-A7D2-D706FBAD8E49}"/>
   </bookViews>
   <sheets>
     <sheet name="Student Information" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="178">
   <si>
     <t>Class 1</t>
   </si>
@@ -537,6 +537,42 @@
   </si>
   <si>
     <t>Know the Variables, review homework</t>
+  </si>
+  <si>
+    <t>Branching 1</t>
+  </si>
+  <si>
+    <t>Simulation and Two Pointers</t>
+  </si>
+  <si>
+    <t>16:00 - 17:30</t>
+  </si>
+  <si>
+    <t>(Online) Simulation and Prefix Sum</t>
+  </si>
+  <si>
+    <t>Class 15</t>
+  </si>
+  <si>
+    <t>Class 16</t>
+  </si>
+  <si>
+    <t>Branching 1, Branching 2</t>
+  </si>
+  <si>
+    <t>Ayden Tsai</t>
+  </si>
+  <si>
+    <t>Melinda Lin</t>
+  </si>
+  <si>
+    <t>King's School</t>
+  </si>
+  <si>
+    <t>aydent1836@gmail.com</t>
+  </si>
+  <si>
+    <t>lijuanlin89@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -1014,15 +1050,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91FB8569-CA3E-974B-8804-A3AC313A4BC3}">
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="3" max="3" width="33.85546875" customWidth="1"/>
-    <col min="4" max="4" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="33.83203125" customWidth="1"/>
+    <col min="4" max="4" width="36.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -1039,7 +1075,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1056,7 +1092,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -1073,7 +1109,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1090,7 +1126,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -1107,7 +1143,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>85</v>
       </c>
@@ -1124,7 +1160,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>90</v>
       </c>
@@ -1141,7 +1177,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>91</v>
       </c>
@@ -1158,7 +1194,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>110</v>
       </c>
@@ -1175,7 +1211,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>87</v>
       </c>
@@ -1192,7 +1228,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>95</v>
       </c>
@@ -1209,7 +1245,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>115</v>
       </c>
@@ -1226,7 +1262,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>102</v>
       </c>
@@ -1243,7 +1279,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>106</v>
       </c>
@@ -1260,7 +1296,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>130</v>
       </c>
@@ -1277,7 +1313,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>131</v>
       </c>
@@ -1294,7 +1330,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>132</v>
       </c>
@@ -1311,7 +1347,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>135</v>
       </c>
@@ -1328,7 +1364,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>133</v>
       </c>
@@ -1345,7 +1381,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>136</v>
       </c>
@@ -1362,7 +1398,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>150</v>
       </c>
@@ -1379,7 +1415,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>153</v>
       </c>
@@ -1393,7 +1429,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>155</v>
       </c>
@@ -1410,7 +1446,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>158</v>
       </c>
@@ -1422,6 +1458,43 @@
       </c>
       <c r="D24" t="s">
         <v>159</v>
+      </c>
+      <c r="E24">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>175</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="E25">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B26">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="E26">
+        <v>2026</v>
       </c>
     </row>
   </sheetData>
@@ -1446,6 +1519,8 @@
     <hyperlink ref="D20" r:id="rId18" xr:uid="{DBB3C7ED-BF02-4317-AAE3-D4789EB2AB81}"/>
     <hyperlink ref="D21" r:id="rId19" xr:uid="{1AC52EE6-8031-4E61-97BC-A16EE2F31BE4}"/>
     <hyperlink ref="D19" r:id="rId20" xr:uid="{5952183A-29A7-409D-93BF-AA0EF92E7186}"/>
+    <hyperlink ref="D25" r:id="rId21" xr:uid="{B7D10D5A-C18F-BB49-B8EE-D11F6CB65EE2}"/>
+    <hyperlink ref="D26" r:id="rId22" xr:uid="{C0986F85-3C11-3B46-B2A7-F42D92FF1B74}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1454,17 +1529,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05115B71-C326-1145-853C-2345070572D9}">
   <dimension ref="A1:P28"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="12.9" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="4" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.35546875" style="3" customWidth="1"/>
-    <col min="4" max="8" width="3.85546875" style="3" customWidth="1"/>
-    <col min="9" max="14" width="15.85546875" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="10.85546875" style="4"/>
+    <col min="3" max="3" width="13.33203125" style="3" customWidth="1"/>
+    <col min="4" max="8" width="3.83203125" style="3" customWidth="1"/>
+    <col min="9" max="14" width="15.83203125" style="3" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="15" customFormat="1" ht="31.75" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" s="15" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>5</v>
       </c>
@@ -1482,7 +1557,7 @@
       <c r="M1" s="14"/>
       <c r="N1" s="14"/>
     </row>
-    <row r="2" spans="1:16" ht="80.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -1522,7 +1597,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -1564,7 +1639,7 @@
       </c>
       <c r="P3" s="8"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
@@ -1593,7 +1668,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>0</v>
       </c>
@@ -1632,7 +1707,7 @@
       </c>
       <c r="P5" s="8"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>26</v>
       </c>
@@ -1659,7 +1734,7 @@
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
@@ -1692,7 +1767,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
@@ -1723,7 +1798,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>26</v>
       </c>
@@ -1756,7 +1831,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>29</v>
       </c>
@@ -1787,7 +1862,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>28</v>
       </c>
@@ -1820,7 +1895,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>31</v>
       </c>
@@ -1853,7 +1928,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>33</v>
       </c>
@@ -1877,7 +1952,7 @@
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>34</v>
       </c>
@@ -1916,7 +1991,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>79</v>
       </c>
@@ -1939,7 +2014,7 @@
       <c r="N15" s="8"/>
       <c r="O15" s="8"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>0</v>
       </c>
@@ -1973,7 +2048,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
@@ -2002,7 +2077,7 @@
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>26</v>
       </c>
@@ -2031,7 +2106,7 @@
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>28</v>
       </c>
@@ -2060,7 +2135,7 @@
       <c r="N19" s="8"/>
       <c r="O19" s="8"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>29</v>
       </c>
@@ -2088,7 +2163,7 @@
       <c r="N20" s="8"/>
       <c r="O20" s="8"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>31</v>
       </c>
@@ -2119,7 +2194,7 @@
       <c r="N21" s="8"/>
       <c r="O21" s="8"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>34</v>
       </c>
@@ -2150,7 +2225,7 @@
       <c r="N22" s="8"/>
       <c r="O22" s="8"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="5"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7"/>
@@ -2162,7 +2237,7 @@
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="5"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7"/>
@@ -2174,7 +2249,7 @@
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="5"/>
       <c r="B25" s="6"/>
       <c r="C25" s="7"/>
@@ -2186,7 +2261,7 @@
       <c r="N25" s="8"/>
       <c r="O25" s="8"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="5"/>
       <c r="B26" s="6"/>
       <c r="C26" s="7"/>
@@ -2198,7 +2273,7 @@
       <c r="N26" s="8"/>
       <c r="O26" s="8"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="5"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7"/>
@@ -2210,7 +2285,7 @@
       <c r="N27" s="8"/>
       <c r="O27" s="8"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="5"/>
       <c r="B28" s="6"/>
       <c r="C28" s="7"/>
@@ -2231,17 +2306,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1940DD8-A835-C84C-9FD6-C7272FA36228}">
   <dimension ref="A1:O28"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="12.9" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="4" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.35546875" style="3" customWidth="1"/>
-    <col min="4" max="7" width="3.85546875" style="3" customWidth="1"/>
-    <col min="8" max="13" width="15.85546875" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="10.85546875" style="4"/>
+    <col min="3" max="3" width="13.33203125" style="3" customWidth="1"/>
+    <col min="4" max="7" width="3.83203125" style="3" customWidth="1"/>
+    <col min="8" max="13" width="15.83203125" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="15" customFormat="1" ht="31.75" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" s="15" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>89</v>
       </c>
@@ -2258,7 +2333,7 @@
       <c r="L1" s="14"/>
       <c r="M1" s="14"/>
     </row>
-    <row r="2" spans="1:15" ht="80.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -2295,7 +2370,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -2327,7 +2402,7 @@
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
@@ -2359,7 +2434,7 @@
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>26</v>
       </c>
@@ -2386,7 +2461,7 @@
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>28</v>
       </c>
@@ -2413,7 +2488,7 @@
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>29</v>
       </c>
@@ -2443,7 +2518,7 @@
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>31</v>
       </c>
@@ -2473,7 +2548,7 @@
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>34</v>
       </c>
@@ -2503,7 +2578,7 @@
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>122</v>
       </c>
@@ -2535,7 +2610,7 @@
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>123</v>
       </c>
@@ -2567,7 +2642,7 @@
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>124</v>
       </c>
@@ -2592,7 +2667,7 @@
       <c r="N12" s="8"/>
       <c r="O12" s="8"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>125</v>
       </c>
@@ -2620,7 +2695,7 @@
       <c r="N13" s="8"/>
       <c r="O13" s="8"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>126</v>
       </c>
@@ -2648,7 +2723,7 @@
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>152</v>
       </c>
@@ -2675,7 +2750,7 @@
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>161</v>
       </c>
@@ -2704,11 +2779,28 @@
       <c r="N16" s="8"/>
       <c r="O16" s="8"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
-      <c r="H17" s="8"/>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B17" s="6">
+        <v>46250</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
@@ -2717,11 +2809,28 @@
       <c r="N17" s="8"/>
       <c r="O17" s="8"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="7"/>
-      <c r="H18" s="8"/>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B18" s="6">
+        <v>46254</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>169</v>
+      </c>
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
@@ -2730,7 +2839,7 @@
       <c r="N18" s="8"/>
       <c r="O18" s="8"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="7"/>
@@ -2742,7 +2851,7 @@
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="7"/>
@@ -2754,7 +2863,7 @@
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7"/>
@@ -2766,7 +2875,7 @@
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="5"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7"/>
@@ -2778,7 +2887,7 @@
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="5"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7"/>
@@ -2790,7 +2899,7 @@
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="5"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7"/>
@@ -2802,7 +2911,7 @@
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="5"/>
       <c r="B25" s="6"/>
       <c r="C25" s="7"/>
@@ -2814,7 +2923,7 @@
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="5"/>
       <c r="B26" s="6"/>
       <c r="C26" s="7"/>
@@ -2826,7 +2935,7 @@
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="5"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7"/>
@@ -2838,7 +2947,7 @@
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="5"/>
       <c r="B28" s="6"/>
       <c r="C28" s="7"/>
@@ -2859,17 +2968,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DFCB767-1FBD-9647-82C4-2908A24D9134}">
   <dimension ref="A1:T28"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="12.9" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" style="4" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.35546875" style="3" customWidth="1"/>
-    <col min="4" max="14" width="3.85546875" style="3" customWidth="1"/>
-    <col min="15" max="18" width="15.85546875" style="3" customWidth="1"/>
-    <col min="19" max="16384" width="10.85546875" style="4"/>
+    <col min="3" max="3" width="13.33203125" style="3" customWidth="1"/>
+    <col min="4" max="14" width="3.83203125" style="3" customWidth="1"/>
+    <col min="15" max="18" width="15.83203125" style="3" customWidth="1"/>
+    <col min="19" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="15" customFormat="1" ht="31.75" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" s="15" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>94</v>
       </c>
@@ -2891,7 +3000,7 @@
       <c r="Q1" s="14"/>
       <c r="R1" s="14"/>
     </row>
-    <row r="2" spans="1:20" ht="80.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:20" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -2943,7 +3052,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -2989,7 +3098,7 @@
       <c r="S3" s="8"/>
       <c r="T3" s="8"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
@@ -3032,7 +3141,7 @@
       <c r="S4" s="8"/>
       <c r="T4" s="8"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>26</v>
       </c>
@@ -3081,29 +3190,96 @@
       <c r="S5" s="8"/>
       <c r="T5" s="8"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="7"/>
-      <c r="O6" s="8"/>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="6">
+        <v>46250</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>166</v>
+      </c>
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
       <c r="S6" s="8"/>
       <c r="T6" s="8"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="7"/>
-      <c r="O7" s="8"/>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="6">
+        <v>46257</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>172</v>
+      </c>
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
       <c r="T7" s="8"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7"/>
@@ -3114,7 +3290,7 @@
       <c r="S8" s="8"/>
       <c r="T8" s="8"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
@@ -3125,7 +3301,7 @@
       <c r="S9" s="8"/>
       <c r="T9" s="8"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7"/>
@@ -3136,7 +3312,7 @@
       <c r="S10" s="8"/>
       <c r="T10" s="8"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7"/>
@@ -3147,7 +3323,7 @@
       <c r="S11" s="8"/>
       <c r="T11" s="8"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7"/>
@@ -3158,7 +3334,7 @@
       <c r="S12" s="8"/>
       <c r="T12" s="8"/>
     </row>
-    <row r="13" spans="1:20" ht="15.9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7"/>
@@ -3169,7 +3345,7 @@
       <c r="S13" s="1"/>
       <c r="T13" s="8"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
@@ -3180,7 +3356,7 @@
       <c r="S14" s="8"/>
       <c r="T14" s="8"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
@@ -3190,7 +3366,7 @@
       <c r="R15" s="8"/>
       <c r="S15" s="8"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="7"/>
@@ -3201,7 +3377,7 @@
       <c r="S16" s="8"/>
       <c r="T16" s="8"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7"/>
@@ -3212,7 +3388,7 @@
       <c r="S17" s="8"/>
       <c r="T17" s="8"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="7"/>
@@ -3223,7 +3399,7 @@
       <c r="S18" s="8"/>
       <c r="T18" s="8"/>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="7"/>
@@ -3233,7 +3409,7 @@
       <c r="R19" s="8"/>
       <c r="S19" s="8"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="7"/>
@@ -3243,7 +3419,7 @@
       <c r="R20" s="8"/>
       <c r="S20" s="8"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7"/>
@@ -3253,7 +3429,7 @@
       <c r="R21" s="8"/>
       <c r="S21" s="8"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" s="5"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7"/>
@@ -3263,7 +3439,7 @@
       <c r="R22" s="8"/>
       <c r="S22" s="8"/>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" s="5"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7"/>
@@ -3273,7 +3449,7 @@
       <c r="R23" s="8"/>
       <c r="S23" s="8"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" s="5"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7"/>
@@ -3283,7 +3459,7 @@
       <c r="R24" s="8"/>
       <c r="S24" s="8"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" s="5"/>
       <c r="B25" s="6"/>
       <c r="C25" s="7"/>
@@ -3293,7 +3469,7 @@
       <c r="R25" s="8"/>
       <c r="S25" s="8"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" s="5"/>
       <c r="B26" s="6"/>
       <c r="C26" s="7"/>
@@ -3303,7 +3479,7 @@
       <c r="R26" s="8"/>
       <c r="S26" s="8"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" s="5"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7"/>
@@ -3313,7 +3489,7 @@
       <c r="R27" s="8"/>
       <c r="S27" s="8"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" s="5"/>
       <c r="B28" s="6"/>
       <c r="C28" s="7"/>
